--- a/資料1/未入帳清單_11504.xlsx
+++ b/資料1/未入帳清單_11504.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -52,9 +52,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <color rgb="00000000"/>
     </font>
   </fonts>
   <fills count="6">
@@ -123,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
@@ -181,9 +178,6 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -582,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1094"/>
+  <dimension ref="A1:K1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="13.69921875" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -594,7 +588,6 @@
     <col width="14.3984375" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
     <col width="10" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
     <col width="10" customWidth="1" style="6" min="11" max="11"/>
-    <col width="12" customWidth="1" style="6" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="6">
@@ -709,11 +702,6 @@
           <t>待確認</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>經辦人</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="6">
       <c r="A7" s="3" t="inlineStr">
@@ -15947,11 +15935,6 @@
         </is>
       </c>
       <c r="K347" s="14" t="n"/>
-      <c r="L347" s="15" t="inlineStr">
-        <is>
-          <t>人工處理</t>
-        </is>
-      </c>
     </row>
     <row r="348" ht="15.6" customHeight="1" s="6">
       <c r="A348" s="3" t="inlineStr">
@@ -37801,11 +37784,6 @@
         </is>
       </c>
       <c r="K836" s="14" t="n"/>
-      <c r="L836" s="22" t="inlineStr">
-        <is>
-          <t>A67（待確認）</t>
-        </is>
-      </c>
     </row>
     <row r="837" ht="15.6" customHeight="1" s="6">
       <c r="A837" s="3" t="inlineStr">
@@ -39161,11 +39139,6 @@
         </is>
       </c>
       <c r="K867" s="14" t="n"/>
-      <c r="L867" s="22" t="inlineStr">
-        <is>
-          <t>許嘉芳</t>
-        </is>
-      </c>
     </row>
     <row r="868" ht="15.6" customHeight="1" s="6">
       <c r="A868" s="3" t="inlineStr">
@@ -42889,11 +42862,6 @@
         </is>
       </c>
       <c r="K950" s="14" t="n"/>
-      <c r="L950" s="22" t="inlineStr">
-        <is>
-          <t>許嘉芳</t>
-        </is>
-      </c>
     </row>
     <row r="951" ht="15.6" customHeight="1" s="6">
       <c r="A951" s="3" t="inlineStr">
@@ -43888,11 +43856,6 @@
         </is>
       </c>
       <c r="K972" s="14" t="n"/>
-      <c r="L972" s="15" t="inlineStr">
-        <is>
-          <t>人工處理</t>
-        </is>
-      </c>
     </row>
     <row r="973" ht="15.6" customHeight="1" s="6">
       <c r="A973" s="3" t="inlineStr">
@@ -45268,11 +45231,6 @@
         </is>
       </c>
       <c r="K1003" s="14" t="n"/>
-      <c r="L1003" s="15" t="inlineStr">
-        <is>
-          <t>人工處理</t>
-        </is>
-      </c>
     </row>
     <row r="1004" ht="15.6" customHeight="1" s="6">
       <c r="A1004" s="3" t="inlineStr">
@@ -47073,11 +47031,6 @@
         </is>
       </c>
       <c r="K1043" s="14" t="n"/>
-      <c r="L1043" s="22" t="inlineStr">
-        <is>
-          <t>沈淑慧</t>
-        </is>
-      </c>
     </row>
     <row r="1044" ht="15.6" customHeight="1" s="6">
       <c r="A1044" s="3" t="inlineStr">
@@ -47348,11 +47301,6 @@
         </is>
       </c>
       <c r="K1049" s="14" t="n"/>
-      <c r="L1049" s="15" t="inlineStr">
-        <is>
-          <t>人工處理</t>
-        </is>
-      </c>
     </row>
     <row r="1050" ht="15.6" customHeight="1" s="6">
       <c r="A1050" s="3" t="inlineStr">
@@ -48608,7 +48556,6 @@
       <c r="J1079" s="16" t="n"/>
       <c r="K1079" s="16" t="n"/>
     </row>
-    <row r="1080"/>
     <row r="1081">
       <c r="A1081" s="17" t="inlineStr">
         <is>
